--- a/SHET/GZLRT001/gzotkllrt2.xlsx
+++ b/SHET/GZLRT001/gzotkllrt2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZ001\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZLRT001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B06E60-5794-4CA1-A772-D68347270654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73A03EB-D581-41B0-AFC9-74A9088ED400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -76,12 +76,6 @@
     <t>X:75, X:80</t>
   </si>
   <si>
-    <t>Проверка правильности работы отключающей ступени ГЗ при введенной блокировке ГЗ АТ откл</t>
-  </si>
-  <si>
-    <t>gzotkl2</t>
-  </si>
-  <si>
     <t>X:75, M5.XB:23</t>
   </si>
   <si>
@@ -110,6 +104,12 @@
   </si>
   <si>
     <t>ТС</t>
+  </si>
+  <si>
+    <t>gzotkllrt2</t>
+  </si>
+  <si>
+    <t>Проверка правильности работы отключающей ступени ГЗ ЛРТ при введенной блокировке ГЗ ЛРТ</t>
   </si>
 </sst>
 </file>
@@ -447,13 +447,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -483,7 +483,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -497,13 +497,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -537,16 +537,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
@@ -557,16 +557,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -577,16 +577,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
@@ -606,7 +606,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -627,7 +627,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -670,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/SHET/GZLRT001/gzotkllrt2.xlsx
+++ b/SHET/GZLRT001/gzotkllrt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZLRT001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73A03EB-D581-41B0-AFC9-74A9088ED400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5406A52D-9F49-4899-A6FE-FD1718692C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -55,45 +55,15 @@
     <t>X:161, X:221</t>
   </si>
   <si>
-    <t>Срабатывание выходного реле при введеном SA1</t>
-  </si>
-  <si>
-    <t>ГЗ АТ откл: Срабатывание</t>
-  </si>
-  <si>
-    <t>ГЗ АТ откл: Отключение</t>
-  </si>
-  <si>
-    <t>ГЗ АТ откл/ ГЗ откл 1 цепь: Срабатывание контакта</t>
-  </si>
-  <si>
     <t>Сброс блокировки ГЗ,ТЗ</t>
   </si>
   <si>
-    <t>ГЗ АТ откл: Блокировка</t>
-  </si>
-  <si>
-    <t>X:75, X:80</t>
-  </si>
-  <si>
-    <t>X:75, M5.XB:23</t>
-  </si>
-  <si>
-    <t>ГЗ АТ откл/ ГЗ откл 1 цепь: Низкая изоляция</t>
-  </si>
-  <si>
     <t>Да*</t>
   </si>
   <si>
     <t>Нет**</t>
   </si>
   <si>
-    <t>*) - возврат после Tбл ГЗ АТ откл</t>
-  </si>
-  <si>
-    <t>**) - срабатывание после Tбл ГЗ АТ откл</t>
-  </si>
-  <si>
     <t>Вход для проверки</t>
   </si>
   <si>
@@ -110,6 +80,36 @@
   </si>
   <si>
     <t>Проверка правильности работы отключающей ступени ГЗ ЛРТ при введенной блокировке ГЗ ЛРТ</t>
+  </si>
+  <si>
+    <t>ГЗ ЛРТ откл/ ГЗ откл 1 цепь: Срабатывание контакта</t>
+  </si>
+  <si>
+    <t>ГЗ ЛРТ откл/ ГЗ откл 1 цепь: Низкая изоляция</t>
+  </si>
+  <si>
+    <t>ГЗ ЛРТ откл: Срабатывание</t>
+  </si>
+  <si>
+    <t>ГЗ ЛРТ откл: Отключение</t>
+  </si>
+  <si>
+    <t>ГЗ ЛРТ откл: Блокировка</t>
+  </si>
+  <si>
+    <t>X:91, X:94</t>
+  </si>
+  <si>
+    <t>X:91, M6.XB:5</t>
+  </si>
+  <si>
+    <t>*) - возврат после Tбл ГЗ ЛРТ откл</t>
+  </si>
+  <si>
+    <t>**) - срабатывание после Tбл ГЗ ЛРТ откл</t>
+  </si>
+  <si>
+    <t>Срабатывание выходного реле</t>
   </si>
 </sst>
 </file>
@@ -447,13 +447,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -477,13 +477,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -497,13 +497,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -520,10 +520,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -537,16 +537,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
@@ -557,16 +557,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -577,16 +577,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
@@ -597,16 +597,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -627,7 +627,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -670,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
